--- a/data/trans_dic/P1413-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1413-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 17,83</t>
+          <t>11,09; 17,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,62</t>
+          <t>4,73; 9,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,78</t>
+          <t>5,48; 11,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 17,81</t>
+          <t>11,91; 17,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,52</t>
+          <t>9,41; 17,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 17,37</t>
+          <t>8,87; 17,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,97</t>
+          <t>5,09; 11,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,1</t>
+          <t>20,12; 26,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,25</t>
+          <t>11,28; 16,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,95</t>
+          <t>7,24; 11,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,2</t>
+          <t>6,18; 10,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 20,86</t>
+          <t>16,82; 21,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,61</t>
+          <t>7,33; 13,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,57</t>
+          <t>5,73; 11,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,85</t>
+          <t>3,67; 8,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 20,33</t>
+          <t>13,47; 20,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,23; 20,89</t>
+          <t>13,48; 21,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 18,28</t>
+          <t>10,51; 18,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 15,55</t>
+          <t>8,77; 15,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,2</t>
+          <t>24,25; 31,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,2</t>
+          <t>11,27; 16,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,52</t>
+          <t>8,7; 13,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,93</t>
+          <t>6,69; 11,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,32</t>
+          <t>19,56; 24,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,62; 22,5</t>
+          <t>15,49; 22,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,02</t>
+          <t>7,74; 12,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,46</t>
+          <t>5,6; 10,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 23,42</t>
+          <t>18,32; 25,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 28,75</t>
+          <t>15,66; 28,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 20,2</t>
+          <t>10,77; 20,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 27,4</t>
+          <t>14,72; 27,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 41,92</t>
+          <t>30,7; 41,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 22,17</t>
+          <t>16,33; 22,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,03</t>
+          <t>9,47; 14,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,66</t>
+          <t>8,58; 13,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 26,98</t>
+          <t>22,92; 29,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,81</t>
+          <t>18,31; 22,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,11</t>
+          <t>9,26; 13,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,82</t>
+          <t>7,53; 10,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 24,31</t>
+          <t>18,75; 23,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,46</t>
+          <t>16,62; 22,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 19,19</t>
+          <t>13,64; 19,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,43</t>
+          <t>10,66; 15,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 64,94</t>
+          <t>24,76; 29,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 21,82</t>
+          <t>18,28; 21,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 14,71</t>
+          <t>11,52; 14,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,27</t>
+          <t>9,47; 12,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,2; 54,4</t>
+          <t>22,0; 25,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,57</t>
+          <t>14,9; 23,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,38</t>
+          <t>6,37; 11,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,74</t>
+          <t>9,61; 14,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,44; 25,91</t>
+          <t>17,69; 24,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 25,1</t>
+          <t>17,86; 24,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,34; 26,51</t>
+          <t>20,0; 26,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,59; 20,16</t>
+          <t>14,52; 20,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,6; 41,51</t>
+          <t>36,7; 42,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,05; 23,52</t>
+          <t>18,01; 23,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 19,58</t>
+          <t>15,23; 19,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 16,66</t>
+          <t>13,17; 16,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,87; 34,3</t>
+          <t>29,94; 34,56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,82</t>
+          <t>0,72; 4,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,41</t>
+          <t>0,78; 5,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,08; 16,41</t>
+          <t>4,59; 15,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 22,63</t>
+          <t>18,1; 22,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,01</t>
+          <t>17,21; 22,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,01</t>
+          <t>11,84; 16,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,49; 33,16</t>
+          <t>27,34; 32,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,93; 18,7</t>
+          <t>14,84; 18,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,19</t>
+          <t>14,25; 18,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 13,01</t>
+          <t>9,32; 12,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 27,99</t>
+          <t>22,95; 28,39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,56</t>
+          <t>14,86; 17,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 10,06</t>
+          <t>8,05; 10,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,24</t>
+          <t>7,29; 9,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,15; 19,32</t>
+          <t>17,45; 20,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,93; 20,66</t>
+          <t>17,96; 20,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,96; 19,42</t>
+          <t>16,84; 19,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,58; 15,17</t>
+          <t>12,68; 15,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,21; 47,15</t>
+          <t>29,54; 32,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,78; 18,7</t>
+          <t>16,81; 18,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,51</t>
+          <t>12,76; 14,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,27; 11,9</t>
+          <t>10,33; 11,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,68; 33,53</t>
+          <t>23,98; 25,89</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73764</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>177481</t>
+          <t>196457</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52942; 84492</t>
+          <t>52528; 83265</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20704; 42062</t>
+          <t>20689; 42215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23580; 46263</t>
+          <t>23522; 48272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59846; 89794</t>
+          <t>65425; 98147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29287; 53726</t>
+          <t>28855; 53227</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28784; 54608</t>
+          <t>27881; 53993</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17459; 38084</t>
+          <t>17661; 38822</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90272; 121078</t>
+          <t>98122; 130986</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87324; 126834</t>
+          <t>88026; 126121</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54353; 89795</t>
+          <t>54415; 87802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46501; 79158</t>
+          <t>47971; 77745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>155400; 198407</t>
+          <t>174474; 218772</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>80374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>103836</t>
+          <t>118324</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>180567</t>
+          <t>198698</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27147; 49946</t>
+          <t>26878; 48668</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24450; 48471</t>
+          <t>24018; 48794</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13267; 33392</t>
+          <t>13843; 32391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62073; 91770</t>
+          <t>64977; 98447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49180; 77671</t>
+          <t>50144; 78766</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35522; 61772</t>
+          <t>35514; 62632</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33249; 57877</t>
+          <t>32654; 57232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89524; 119174</t>
+          <t>102467; 134532</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82598; 119688</t>
+          <t>83231; 119895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66457; 102352</t>
+          <t>65826; 102396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50385; 81932</t>
+          <t>50155; 83527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>159001; 202684</t>
+          <t>176941; 223547</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93044</t>
+          <t>102901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61350</t>
+          <t>67845</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>154393</t>
+          <t>170746</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84706; 122049</t>
+          <t>84020; 120991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48978; 81961</t>
+          <t>48703; 80193</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29816; 54571</t>
+          <t>29250; 55142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36674; 156361</t>
+          <t>86256; 120761</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26337; 48241</t>
+          <t>26282; 47083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28702; 52547</t>
+          <t>28015; 53111</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24790; 45526</t>
+          <t>24450; 46416</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51270; 69973</t>
+          <t>57552; 78281</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116220; 157461</t>
+          <t>115956; 156245</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86219; 124834</t>
+          <t>84250; 126424</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60415; 93979</t>
+          <t>59037; 92823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72349; 225099</t>
+          <t>150843; 191786</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222363</t>
+          <t>237434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>412223</t>
+          <t>234408</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>634585</t>
+          <t>471842</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223906; 282438</t>
+          <t>226733; 282954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107709; 151895</t>
+          <t>107326; 152921</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86716; 124337</t>
+          <t>86580; 125729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197995; 250977</t>
+          <t>211776; 265977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>116810; 160424</t>
+          <t>118688; 159556</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104239; 146747</t>
+          <t>104290; 147203</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86148; 127419</t>
+          <t>88065; 127581</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>251499; 635144</t>
+          <t>213215; 257302</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>355575; 426062</t>
+          <t>356913; 423660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>224667; 283065</t>
+          <t>221621; 283063</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>185482; 242337</t>
+          <t>187167; 243044</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>466445; 1093781</t>
+          <t>437925; 506368</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104202</t>
+          <t>118464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>302386</t>
+          <t>329782</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>406588</t>
+          <t>448246</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54348; 82625</t>
+          <t>52220; 80945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32852; 58083</t>
+          <t>32517; 58797</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59686; 91494</t>
+          <t>59681; 92129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87400; 122813</t>
+          <t>100285; 141315</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>103514; 142743</t>
+          <t>101607; 141719</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154608; 201518</t>
+          <t>152048; 199690</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107734; 148837</t>
+          <t>107161; 150176</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>231596; 348234</t>
+          <t>304668; 351879</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>165954; 216235</t>
+          <t>165577; 215399</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192124; 248801</t>
+          <t>193597; 250388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>174490; 226375</t>
+          <t>178966; 230365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>326609; 450374</t>
+          <t>418299; 482892</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>230092</t>
+          <t>253661</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>251195</t>
+          <t>274254</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1953; 11384</t>
+          <t>2144; 12083</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2052; 14426</t>
+          <t>2071; 15798</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 5693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9818; 39461</t>
+          <t>10890; 37113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>227550; 282573</t>
+          <t>226087; 281101</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>190323; 244135</t>
+          <t>190911; 245673</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>126112; 173183</t>
+          <t>128131; 175329</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>209148; 252209</t>
+          <t>230614; 276753</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>230949; 289298</t>
+          <t>229542; 286002</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193149; 250311</t>
+          <t>196118; 250973</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129175; 178157</t>
+          <t>127575; 177477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>225329; 280252</t>
+          <t>248057; 306874</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>591205</t>
+          <t>641561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1213605</t>
+          <t>1118682</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1804810</t>
+          <t>1760243</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>490166; 574085</t>
+          <t>486113; 572233</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275438; 344249</t>
+          <t>275511; 343623</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>247317; 312925</t>
+          <t>246709; 313096</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>443169; 651149</t>
+          <t>599590; 690038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>605538; 698028</t>
+          <t>606835; 697865</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>601542; 688971</t>
+          <t>597421; 690951</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>444384; 535674</t>
+          <t>447767; 535297</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1043690; 1684771</t>
+          <t>1072953; 1167123</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1115607; 1243162</t>
+          <t>1117848; 1239993</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>891995; 1010933</t>
+          <t>889414; 1011123</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>710125; 823016</t>
+          <t>714764; 824035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1574840; 2328210</t>
+          <t>1695368; 1829955</t>
         </is>
       </c>
     </row>
